--- a/public/import-templates/employees_import_template.xlsx
+++ b/public/import-templates/employees_import_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project_Web\Final_Year_Btech_2026\Prototype\multipos_prototype_v0.1\public\import-templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project_Web\Final_Year_Btech_2026\Prototype\Test-Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9480FC97-7475-4E4C-B515-3C3AC1A4CDE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2DE797-8E9B-485D-B4BC-D499CE17E769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C83875D7-564F-4117-A0A5-4E51A0F7749F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="133">
   <si>
     <t>firstName</t>
   </si>
@@ -63,9 +63,6 @@
     <t>role</t>
   </si>
   <si>
-    <t>shopId</t>
-  </si>
-  <si>
     <t>hasSystemAccess</t>
   </si>
   <si>
@@ -90,14 +87,362 @@
     <t>CASHIER</t>
   </si>
   <si>
-    <t>null</t>
+    <t>MANAGER</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>Mensah</t>
+  </si>
+  <si>
+    <t>sarah.mensah@example.com</t>
+  </si>
+  <si>
+    <t>Store Keeper</t>
+  </si>
+  <si>
+    <t>45 Ring Road</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Owusu</t>
+  </si>
+  <si>
+    <t>michael.owusu@example.com</t>
+  </si>
+  <si>
+    <t>Cashier</t>
+  </si>
+  <si>
+    <t>78 Oxford St</t>
+  </si>
+  <si>
+    <t>Linda</t>
+  </si>
+  <si>
+    <t>Asare</t>
+  </si>
+  <si>
+    <t>linda.asare@example.com</t>
+  </si>
+  <si>
+    <t>Supervisor</t>
+  </si>
+  <si>
+    <t>12 Mango Ave</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Boateng</t>
+  </si>
+  <si>
+    <t>daniel.boateng@example.com</t>
+  </si>
+  <si>
+    <t>Inventory Officer</t>
+  </si>
+  <si>
+    <t>90 Palm St</t>
+  </si>
+  <si>
+    <t>ADMIN</t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t>Agyeman</t>
+  </si>
+  <si>
+    <t>grace.agyeman@example.com</t>
+  </si>
+  <si>
+    <t>Sales Associate</t>
+  </si>
+  <si>
+    <t>15 Sunset Blvd</t>
+  </si>
+  <si>
+    <t>Samuel</t>
+  </si>
+  <si>
+    <t>Tetteh</t>
+  </si>
+  <si>
+    <t>samuel.tetteh@example.com</t>
+  </si>
+  <si>
+    <t>Branch Manager</t>
+  </si>
+  <si>
+    <t>201 Lake Rd</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>Koomson</t>
+  </si>
+  <si>
+    <t>patricia.koomson@example.com</t>
+  </si>
+  <si>
+    <t>Customer Service</t>
+  </si>
+  <si>
+    <t>66 Market St</t>
+  </si>
+  <si>
+    <t>Emmanuel</t>
+  </si>
+  <si>
+    <t>Darko</t>
+  </si>
+  <si>
+    <t>emmanuel.darko@example.com</t>
+  </si>
+  <si>
+    <t>Security Officer</t>
+  </si>
+  <si>
+    <t>7 Freedom Way</t>
+  </si>
+  <si>
+    <t>Joyce</t>
+  </si>
+  <si>
+    <t>Amponsah</t>
+  </si>
+  <si>
+    <t>joyce.amponsah@example.com</t>
+  </si>
+  <si>
+    <t>Sales Executive</t>
+  </si>
+  <si>
+    <t>88 High St</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>Addai</t>
+  </si>
+  <si>
+    <t>richard.addai@example.com</t>
+  </si>
+  <si>
+    <t>Procurement Officer</t>
+  </si>
+  <si>
+    <t>19 Airport Rd</t>
+  </si>
+  <si>
+    <t>Felicia</t>
+  </si>
+  <si>
+    <t>Nyarko</t>
+  </si>
+  <si>
+    <t>felicia.nyarko@example.com</t>
+  </si>
+  <si>
+    <t>Receptionist</t>
+  </si>
+  <si>
+    <t>55 King St</t>
+  </si>
+  <si>
+    <t>Kwame</t>
+  </si>
+  <si>
+    <t>Ofori</t>
+  </si>
+  <si>
+    <t>kwame.ofori@example.com</t>
+  </si>
+  <si>
+    <t>Warehouse Manager</t>
+  </si>
+  <si>
+    <t>300 Industrial Area</t>
+  </si>
+  <si>
+    <t>Esther</t>
+  </si>
+  <si>
+    <t>Baah</t>
+  </si>
+  <si>
+    <t>esther.baah@example.com</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>11 Finance Ave</t>
+  </si>
+  <si>
+    <t>Nathaniel</t>
+  </si>
+  <si>
+    <t>Quaye</t>
+  </si>
+  <si>
+    <t>nathaniel.quaye@example.com</t>
+  </si>
+  <si>
+    <t>IT Support</t>
+  </si>
+  <si>
+    <t>99 Tech Park</t>
+  </si>
+  <si>
+    <t>Angela</t>
+  </si>
+  <si>
+    <t>Frimpong</t>
+  </si>
+  <si>
+    <t>angela.frimpong@example.com</t>
+  </si>
+  <si>
+    <t>Sales Rep</t>
+  </si>
+  <si>
+    <t>24 Spintex Rd</t>
+  </si>
+  <si>
+    <t>Kelvin</t>
+  </si>
+  <si>
+    <t>Yeboah</t>
+  </si>
+  <si>
+    <t>kelvin.yeboah@example.com</t>
+  </si>
+  <si>
+    <t>Assistant Manager</t>
+  </si>
+  <si>
+    <t>17 Liberation Rd</t>
+  </si>
+  <si>
+    <t>Mabel</t>
+  </si>
+  <si>
+    <t>Ansah</t>
+  </si>
+  <si>
+    <t>mabel.ansah@example.com</t>
+  </si>
+  <si>
+    <t>Front Desk Officer</t>
+  </si>
+  <si>
+    <t>63 Castle Rd</t>
+  </si>
+  <si>
+    <t>Victor</t>
+  </si>
+  <si>
+    <t>Adjei</t>
+  </si>
+  <si>
+    <t>victor.adjei@example.com</t>
+  </si>
+  <si>
+    <t>Operations Lead</t>
+  </si>
+  <si>
+    <t>82 Harbour St</t>
+  </si>
+  <si>
+    <t>Priscilla</t>
+  </si>
+  <si>
+    <t>Owusuaa</t>
+  </si>
+  <si>
+    <t>priscilla.owusuaa@example.com</t>
+  </si>
+  <si>
+    <t>Shop Attendant</t>
+  </si>
+  <si>
+    <t>9 Coconut Grove</t>
+  </si>
+  <si>
+    <t>0249876543</t>
+  </si>
+  <si>
+    <t>0203344556</t>
+  </si>
+  <si>
+    <t>0556677889</t>
+  </si>
+  <si>
+    <t>0279988776</t>
+  </si>
+  <si>
+    <t>0245551122</t>
+  </si>
+  <si>
+    <t>0501122334</t>
+  </si>
+  <si>
+    <t>0544433221</t>
+  </si>
+  <si>
+    <t>0209988112</t>
+  </si>
+  <si>
+    <t>0267744110</t>
+  </si>
+  <si>
+    <t>0553322114</t>
+  </si>
+  <si>
+    <t>0247766554</t>
+  </si>
+  <si>
+    <t>0276611448</t>
+  </si>
+  <si>
+    <t>0504455667</t>
+  </si>
+  <si>
+    <t>0241199887</t>
+  </si>
+  <si>
+    <t>0551239988</t>
+  </si>
+  <si>
+    <t>0207654321</t>
+  </si>
+  <si>
+    <t>0248887766</t>
+  </si>
+  <si>
+    <t>0271112233</t>
+  </si>
+  <si>
+    <t>0509988771</t>
+  </si>
+  <si>
+    <t>currentShopId</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,8 +458,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -127,8 +486,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -136,21 +501,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF6600"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -479,92 +886,685 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1A82FA9-61CC-4CDD-B48C-4ECBD92830DE}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="15.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.26953125" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.36328125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="6.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.81640625" style="1"/>
+    <col min="18" max="18" width="8.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="15.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" s="6">
+        <v>32888</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="7"/>
+      <c r="J2" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="6">
+        <v>33685</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2">
-        <v>32888</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I3" s="7"/>
+      <c r="J3" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="6">
+        <v>34890</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="6">
+        <v>32452</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
+      <c r="I5" s="7"/>
+      <c r="J5" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="6">
+        <v>33377</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="6">
+        <v>35310</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="6">
+        <v>31411</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="6">
+        <v>34503</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="J9" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="6">
+        <v>31881</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="6">
+        <v>34208</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="7"/>
+      <c r="J11" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="6">
+        <v>32790</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="6">
+        <v>35472</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="6">
+        <v>30682</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="J14" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="6">
+        <v>33061</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="J15" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="6">
+        <v>33749</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="7"/>
+      <c r="J16" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="6">
+        <v>34801</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="7"/>
+      <c r="J17" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18" s="6">
+        <v>32395</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="J18" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G19" s="6">
+        <v>35230</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="7"/>
+      <c r="J19" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G20" s="6">
+        <v>31839</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="J20" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G21" s="6">
+        <v>36149</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="7"/>
+      <c r="J21" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" display="mailto:john.doe@example.com" xr:uid="{51D01141-443D-41E0-AC2F-5F98CA4C0562}"/>
+    <hyperlink ref="C3" r:id="rId2" display="mailto:sarah.mensah@example.com" xr:uid="{61B44330-5E74-47A0-BD6A-46F5E9829869}"/>
+    <hyperlink ref="C4" r:id="rId3" display="mailto:michael.owusu@example.com" xr:uid="{00D31E31-69E7-4446-A03C-35A7D9D0F729}"/>
+    <hyperlink ref="C5" r:id="rId4" display="mailto:linda.asare@example.com" xr:uid="{9916FAD0-7EB3-44B4-AC91-FE1B3260D72A}"/>
+    <hyperlink ref="C6" r:id="rId5" display="mailto:daniel.boateng@example.com" xr:uid="{69DA64EA-5726-4BAD-BE21-0FB2B3396143}"/>
+    <hyperlink ref="C7" r:id="rId6" display="mailto:grace.agyeman@example.com" xr:uid="{5FA40230-1EBC-41C6-A164-1332B10290BD}"/>
+    <hyperlink ref="C8" r:id="rId7" display="mailto:samuel.tetteh@example.com" xr:uid="{375DE0E8-4FC4-4F0E-B136-B4B8D5DA5DD1}"/>
+    <hyperlink ref="C9" r:id="rId8" display="mailto:patricia.koomson@example.com" xr:uid="{5B1DAC3E-0CE4-4FE7-83FC-99B503D95CF5}"/>
+    <hyperlink ref="C10" r:id="rId9" display="mailto:emmanuel.darko@example.com" xr:uid="{B1442BAF-CCD2-4D88-A9B7-3EFC85CA0EFF}"/>
+    <hyperlink ref="C11" r:id="rId10" display="mailto:joyce.amponsah@example.com" xr:uid="{39FE612E-5172-4202-8352-52E5ABF50D5B}"/>
+    <hyperlink ref="C12" r:id="rId11" display="mailto:richard.addai@example.com" xr:uid="{9AB5A9BB-D965-4CB1-99B0-16E5646611FF}"/>
+    <hyperlink ref="C13" r:id="rId12" display="mailto:felicia.nyarko@example.com" xr:uid="{4865602C-CEE1-449A-B4B5-7C33A5F791F1}"/>
+    <hyperlink ref="C14" r:id="rId13" display="mailto:kwame.ofori@example.com" xr:uid="{C8C347C0-E71D-4F23-BAC7-961F0A5A4C92}"/>
+    <hyperlink ref="C15" r:id="rId14" display="mailto:esther.baah@example.com" xr:uid="{B62B6209-E1AD-4B3B-9018-D16D6E043477}"/>
+    <hyperlink ref="C16" r:id="rId15" display="mailto:nathaniel.quaye@example.com" xr:uid="{F94E3D1C-07AA-4231-A8D3-355E1E15182B}"/>
+    <hyperlink ref="C17" r:id="rId16" display="mailto:angela.frimpong@example.com" xr:uid="{D7335134-D21D-46DC-8F3D-E81319406D03}"/>
+    <hyperlink ref="C18" r:id="rId17" display="mailto:kelvin.yeboah@example.com" xr:uid="{BFB6048C-7D1C-4989-9846-497410D81FAD}"/>
+    <hyperlink ref="C19" r:id="rId18" display="mailto:mabel.ansah@example.com" xr:uid="{F7CEB4B4-993E-4A34-90D6-898893052F66}"/>
+    <hyperlink ref="C20" r:id="rId19" display="mailto:victor.adjei@example.com" xr:uid="{E79942B2-4302-464D-9D7D-682F09E2A24B}"/>
+    <hyperlink ref="C21" r:id="rId20" display="mailto:priscilla.owusuaa@example.com" xr:uid="{9575D019-8A31-41F6-8BE5-E4852442DB67}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
